--- a/data/June 2024 Ad Hoc/Maternal  mortality ratio_western districts.xlsx
+++ b/data/June 2024 Ad Hoc/Maternal  mortality ratio_western districts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PIMPA.SAWULU\Downloads\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PIMPA.SAWULU\Documents\E4H-Zambia\data\June 2024 Ad Hoc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47434C7-676B-455D-8DF4-7CDCF93CA9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D10DED-3723-4F5A-89A4-E409E3D333A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{58B0EE6E-B82B-4C9A-AB2A-F089AC76CBCC}"/>
   </bookViews>
@@ -95,19 +95,19 @@
     <t>Sioma</t>
   </si>
   <si>
-    <t>October 2019 - September 2020</t>
-  </si>
-  <si>
-    <t>October 2023 - September 2024</t>
-  </si>
-  <si>
-    <t>October 2020 - September 2021</t>
-  </si>
-  <si>
-    <t>October 2022 - September 2023</t>
-  </si>
-  <si>
-    <t>October 2021 - September 2022</t>
+    <t>FY2020</t>
+  </si>
+  <si>
+    <t>FY2024</t>
+  </si>
+  <si>
+    <t>FY2021</t>
+  </si>
+  <si>
+    <t>FY2023</t>
+  </si>
+  <si>
+    <t>FY2022</t>
   </si>
 </sst>
 </file>

--- a/data/June 2024 Ad Hoc/Maternal  mortality ratio_western districts.xlsx
+++ b/data/June 2024 Ad Hoc/Maternal  mortality ratio_western districts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PIMPA.SAWULU\Documents\E4H-Zambia\data\June 2024 Ad Hoc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D10DED-3723-4F5A-89A4-E409E3D333A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C57D09-E7AD-444D-8B59-82400CD544D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{58B0EE6E-B82B-4C9A-AB2A-F089AC76CBCC}"/>
   </bookViews>
@@ -751,65 +751,65 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>232.25</v>
+        <v>75.38</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>162.38999999999999</v>
+        <v>200.4</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>128.91</v>
+        <v>66.58</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>162.18</v>
+        <v>51.53</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>70.64</v>
+        <v>83.47</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1">
-        <v>75.38</v>
+        <v>129.03</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -817,131 +817,131 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B9" s="1">
-        <v>96.62</v>
+        <v>75.08</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1">
-        <v>91.05</v>
+        <v>121.95</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1">
-        <v>45.8</v>
+        <v>16</v>
+      </c>
+      <c r="B11" s="2">
+        <v>88.03</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B12" s="1">
-        <v>153.49</v>
+        <v>162.38999999999999</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13" s="1">
-        <v>52.22</v>
+        <v>96.62</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1">
-        <v>152.15</v>
+        <v>82.99</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1">
-        <v>42.41</v>
+        <v>168.32</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B16" s="1">
-        <v>200.4</v>
+        <v>253.38</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1">
-        <v>151.52000000000001</v>
+        <v>227.53</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>44.66</v>
+        <v>219.39</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>37.94</v>
+        <v>200.88</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="1">
-        <v>82.99</v>
+        <v>14</v>
+      </c>
+      <c r="B20" s="2">
+        <v>103.09</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
@@ -949,32 +949,32 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="1">
-        <v>66.58</v>
+        <v>16</v>
+      </c>
+      <c r="B21" s="2">
+        <v>72.31</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="1">
-        <v>51.53</v>
+        <v>17</v>
+      </c>
+      <c r="B22" s="2">
+        <v>85.03</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B23" s="1">
-        <v>168.51</v>
+        <v>162.18</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
@@ -982,46 +982,46 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B24" s="1">
-        <v>168.32</v>
+        <v>45.8</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B25" s="1">
-        <v>322</v>
+        <v>52.22</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" s="1">
-        <v>465.12</v>
+        <v>37.94</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B27" s="1">
-        <v>83.47</v>
+        <v>168.51</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.5">
@@ -1037,109 +1037,109 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B29" s="1">
-        <v>69.739999999999995</v>
+        <v>80.06</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" s="1">
-        <v>253.38</v>
+        <v>79.709999999999994</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="1">
-        <v>187.62</v>
+        <v>14</v>
+      </c>
+      <c r="B31" s="2">
+        <v>51.2</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="1">
-        <v>129.03</v>
+        <v>15</v>
+      </c>
+      <c r="B32" s="2">
+        <v>121.88</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" s="1">
-        <v>60.94</v>
+        <v>16</v>
+      </c>
+      <c r="B33" s="2">
+        <v>76.28</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="1">
-        <v>66.760000000000005</v>
+        <v>17</v>
+      </c>
+      <c r="B34" s="2">
+        <v>82.1</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B35" s="1">
-        <v>227.53</v>
+        <v>128.91</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B36" s="1">
-        <v>27.04</v>
+        <v>70.64</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B37" s="1">
-        <v>219.39</v>
+        <v>153.49</v>
       </c>
       <c r="C37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B38" s="1">
-        <v>37.81</v>
+        <v>42.41</v>
       </c>
       <c r="C38" t="s">
         <v>21</v>
@@ -1147,21 +1147,21 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B39" s="1">
-        <v>80.06</v>
+        <v>44.66</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B40" s="1">
-        <v>153.49</v>
+        <v>322</v>
       </c>
       <c r="C40" t="s">
         <v>21</v>
@@ -1169,57 +1169,57 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B41" s="1">
-        <v>79.709999999999994</v>
+        <v>69.739999999999995</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B42" s="1">
-        <v>200.88</v>
+        <v>187.62</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B43" s="1">
-        <v>205.9</v>
+        <v>60.94</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B44" s="1">
-        <v>75.08</v>
+        <v>37.81</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B45" s="1">
-        <v>121.95</v>
+        <v>153.49</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.5">
@@ -1235,43 +1235,43 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B47" s="2">
-        <v>103.09</v>
+        <v>53.53</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B48" s="2">
-        <v>98.18</v>
+        <v>233.83</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>14</v>
-      </c>
-      <c r="B49" s="2">
-        <v>51.2</v>
+        <v>3</v>
+      </c>
+      <c r="B49" s="1">
+        <v>232.25</v>
       </c>
       <c r="C49" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" s="2">
-        <v>119.76</v>
+        <v>4</v>
+      </c>
+      <c r="B50" s="1">
+        <v>91.05</v>
       </c>
       <c r="C50" t="s">
         <v>19</v>
@@ -1279,43 +1279,43 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" s="2">
-        <v>53.53</v>
+        <v>6</v>
+      </c>
+      <c r="B51" s="1">
+        <v>152.15</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" s="2">
-        <v>121.88</v>
+        <v>7</v>
+      </c>
+      <c r="B52" s="1">
+        <v>151.52000000000001</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>16</v>
-      </c>
-      <c r="B53" s="2">
-        <v>72.31</v>
+        <v>8</v>
+      </c>
+      <c r="B53" s="1">
+        <v>465.12</v>
       </c>
       <c r="C53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>16</v>
-      </c>
-      <c r="B54" s="2">
-        <v>65.319999999999993</v>
+        <v>11</v>
+      </c>
+      <c r="B54" s="1">
+        <v>66.760000000000005</v>
       </c>
       <c r="C54" t="s">
         <v>19</v>
@@ -1323,60 +1323,63 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>16</v>
-      </c>
-      <c r="B55" s="2">
-        <v>88.03</v>
+        <v>12</v>
+      </c>
+      <c r="B55" s="1">
+        <v>27.04</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>16</v>
-      </c>
-      <c r="B56" s="2">
-        <v>76.28</v>
+        <v>13</v>
+      </c>
+      <c r="B56" s="1">
+        <v>205.9</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B57" s="2">
-        <v>85.03</v>
+        <v>98.18</v>
       </c>
       <c r="C57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B58" s="2">
-        <v>233.83</v>
+        <v>119.76</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B59" s="2">
-        <v>82.1</v>
+        <v>65.319999999999993</v>
       </c>
       <c r="C59" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C59">
+    <sortCondition ref="C2:C59"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/June 2024 Ad Hoc/Maternal  mortality ratio_western districts.xlsx
+++ b/data/June 2024 Ad Hoc/Maternal  mortality ratio_western districts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PIMPA.SAWULU\Documents\E4H-Zambia\data\June 2024 Ad Hoc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C57D09-E7AD-444D-8B59-82400CD544D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F8891B-3188-4BA5-A787-2D365ACD6640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{58B0EE6E-B82B-4C9A-AB2A-F089AC76CBCC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="18">
   <si>
     <t>period</t>
   </si>
@@ -93,21 +93,6 @@
   </si>
   <si>
     <t>Sioma</t>
-  </si>
-  <si>
-    <t>FY2020</t>
-  </si>
-  <si>
-    <t>FY2024</t>
-  </si>
-  <si>
-    <t>FY2021</t>
-  </si>
-  <si>
-    <t>FY2023</t>
-  </si>
-  <si>
-    <t>FY2022</t>
   </si>
 </sst>
 </file>
@@ -745,8 +730,8 @@
       <c r="B2" s="1">
         <v>65.55</v>
       </c>
-      <c r="C2" t="s">
-        <v>18</v>
+      <c r="C2">
+        <v>2020</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.5">
@@ -756,8 +741,8 @@
       <c r="B3" s="1">
         <v>75.38</v>
       </c>
-      <c r="C3" t="s">
-        <v>18</v>
+      <c r="C3">
+        <v>2020</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.5">
@@ -767,8 +752,8 @@
       <c r="B4" s="1">
         <v>200.4</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
+      <c r="C4">
+        <v>2020</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.5">
@@ -778,8 +763,8 @@
       <c r="B5" s="1">
         <v>66.58</v>
       </c>
-      <c r="C5" t="s">
-        <v>18</v>
+      <c r="C5">
+        <v>2020</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.5">
@@ -789,8 +774,8 @@
       <c r="B6" s="1">
         <v>51.53</v>
       </c>
-      <c r="C6" t="s">
-        <v>18</v>
+      <c r="C6">
+        <v>2020</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.5">
@@ -800,8 +785,8 @@
       <c r="B7" s="1">
         <v>83.47</v>
       </c>
-      <c r="C7" t="s">
-        <v>18</v>
+      <c r="C7">
+        <v>2020</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.5">
@@ -811,8 +796,8 @@
       <c r="B8" s="1">
         <v>129.03</v>
       </c>
-      <c r="C8" t="s">
-        <v>18</v>
+      <c r="C8">
+        <v>2020</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.5">
@@ -822,8 +807,8 @@
       <c r="B9" s="1">
         <v>75.08</v>
       </c>
-      <c r="C9" t="s">
-        <v>18</v>
+      <c r="C9">
+        <v>2020</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.5">
@@ -833,8 +818,8 @@
       <c r="B10" s="1">
         <v>121.95</v>
       </c>
-      <c r="C10" t="s">
-        <v>18</v>
+      <c r="C10">
+        <v>2020</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.5">
@@ -844,8 +829,8 @@
       <c r="B11" s="2">
         <v>88.03</v>
       </c>
-      <c r="C11" t="s">
-        <v>18</v>
+      <c r="C11">
+        <v>2020</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.5">
@@ -855,8 +840,8 @@
       <c r="B12" s="1">
         <v>162.38999999999999</v>
       </c>
-      <c r="C12" t="s">
-        <v>20</v>
+      <c r="C12">
+        <v>2021</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.5">
@@ -866,8 +851,8 @@
       <c r="B13" s="1">
         <v>96.62</v>
       </c>
-      <c r="C13" t="s">
-        <v>20</v>
+      <c r="C13">
+        <v>2021</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.5">
@@ -877,8 +862,8 @@
       <c r="B14" s="1">
         <v>82.99</v>
       </c>
-      <c r="C14" t="s">
-        <v>20</v>
+      <c r="C14">
+        <v>2021</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.5">
@@ -888,8 +873,8 @@
       <c r="B15" s="1">
         <v>168.32</v>
       </c>
-      <c r="C15" t="s">
-        <v>20</v>
+      <c r="C15">
+        <v>2021</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.5">
@@ -899,8 +884,8 @@
       <c r="B16" s="1">
         <v>253.38</v>
       </c>
-      <c r="C16" t="s">
-        <v>20</v>
+      <c r="C16">
+        <v>2021</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.5">
@@ -910,8 +895,8 @@
       <c r="B17" s="1">
         <v>227.53</v>
       </c>
-      <c r="C17" t="s">
-        <v>20</v>
+      <c r="C17">
+        <v>2021</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.5">
@@ -921,8 +906,8 @@
       <c r="B18" s="1">
         <v>219.39</v>
       </c>
-      <c r="C18" t="s">
-        <v>20</v>
+      <c r="C18">
+        <v>2021</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.5">
@@ -932,8 +917,8 @@
       <c r="B19" s="1">
         <v>200.88</v>
       </c>
-      <c r="C19" t="s">
-        <v>20</v>
+      <c r="C19">
+        <v>2021</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.5">
@@ -943,8 +928,8 @@
       <c r="B20" s="2">
         <v>103.09</v>
       </c>
-      <c r="C20" t="s">
-        <v>20</v>
+      <c r="C20">
+        <v>2021</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.5">
@@ -954,8 +939,8 @@
       <c r="B21" s="2">
         <v>72.31</v>
       </c>
-      <c r="C21" t="s">
-        <v>20</v>
+      <c r="C21">
+        <v>2021</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.5">
@@ -965,8 +950,8 @@
       <c r="B22" s="2">
         <v>85.03</v>
       </c>
-      <c r="C22" t="s">
-        <v>20</v>
+      <c r="C22">
+        <v>2021</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.5">
@@ -976,8 +961,8 @@
       <c r="B23" s="1">
         <v>162.18</v>
       </c>
-      <c r="C23" t="s">
-        <v>22</v>
+      <c r="C23">
+        <v>2022</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.5">
@@ -987,8 +972,8 @@
       <c r="B24" s="1">
         <v>45.8</v>
       </c>
-      <c r="C24" t="s">
-        <v>22</v>
+      <c r="C24">
+        <v>2022</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.5">
@@ -998,8 +983,8 @@
       <c r="B25" s="1">
         <v>52.22</v>
       </c>
-      <c r="C25" t="s">
-        <v>22</v>
+      <c r="C25">
+        <v>2022</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.5">
@@ -1009,8 +994,8 @@
       <c r="B26" s="1">
         <v>37.94</v>
       </c>
-      <c r="C26" t="s">
-        <v>22</v>
+      <c r="C26">
+        <v>2022</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.5">
@@ -1020,8 +1005,8 @@
       <c r="B27" s="1">
         <v>168.51</v>
       </c>
-      <c r="C27" t="s">
-        <v>22</v>
+      <c r="C27">
+        <v>2022</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.5">
@@ -1031,8 +1016,8 @@
       <c r="B28" s="1">
         <v>76.22</v>
       </c>
-      <c r="C28" t="s">
-        <v>22</v>
+      <c r="C28">
+        <v>2022</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.5">
@@ -1042,8 +1027,8 @@
       <c r="B29" s="1">
         <v>80.06</v>
       </c>
-      <c r="C29" t="s">
-        <v>22</v>
+      <c r="C29">
+        <v>2022</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.5">
@@ -1053,8 +1038,8 @@
       <c r="B30" s="1">
         <v>79.709999999999994</v>
       </c>
-      <c r="C30" t="s">
-        <v>22</v>
+      <c r="C30">
+        <v>2022</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.5">
@@ -1064,8 +1049,8 @@
       <c r="B31" s="2">
         <v>51.2</v>
       </c>
-      <c r="C31" t="s">
-        <v>22</v>
+      <c r="C31">
+        <v>2022</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.5">
@@ -1075,8 +1060,8 @@
       <c r="B32" s="2">
         <v>121.88</v>
       </c>
-      <c r="C32" t="s">
-        <v>22</v>
+      <c r="C32">
+        <v>2022</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.5">
@@ -1086,8 +1071,8 @@
       <c r="B33" s="2">
         <v>76.28</v>
       </c>
-      <c r="C33" t="s">
-        <v>22</v>
+      <c r="C33">
+        <v>2022</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.5">
@@ -1097,8 +1082,8 @@
       <c r="B34" s="2">
         <v>82.1</v>
       </c>
-      <c r="C34" t="s">
-        <v>22</v>
+      <c r="C34">
+        <v>2022</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.5">
@@ -1108,8 +1093,8 @@
       <c r="B35" s="1">
         <v>128.91</v>
       </c>
-      <c r="C35" t="s">
-        <v>21</v>
+      <c r="C35">
+        <v>2023</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.5">
@@ -1119,8 +1104,8 @@
       <c r="B36" s="1">
         <v>70.64</v>
       </c>
-      <c r="C36" t="s">
-        <v>21</v>
+      <c r="C36">
+        <v>2023</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.5">
@@ -1130,8 +1115,8 @@
       <c r="B37" s="1">
         <v>153.49</v>
       </c>
-      <c r="C37" t="s">
-        <v>21</v>
+      <c r="C37">
+        <v>2023</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.5">
@@ -1141,8 +1126,8 @@
       <c r="B38" s="1">
         <v>42.41</v>
       </c>
-      <c r="C38" t="s">
-        <v>21</v>
+      <c r="C38">
+        <v>2023</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.5">
@@ -1152,8 +1137,8 @@
       <c r="B39" s="1">
         <v>44.66</v>
       </c>
-      <c r="C39" t="s">
-        <v>21</v>
+      <c r="C39">
+        <v>2023</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.5">
@@ -1163,8 +1148,8 @@
       <c r="B40" s="1">
         <v>322</v>
       </c>
-      <c r="C40" t="s">
-        <v>21</v>
+      <c r="C40">
+        <v>2023</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.5">
@@ -1174,8 +1159,8 @@
       <c r="B41" s="1">
         <v>69.739999999999995</v>
       </c>
-      <c r="C41" t="s">
-        <v>21</v>
+      <c r="C41">
+        <v>2023</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.5">
@@ -1185,8 +1170,8 @@
       <c r="B42" s="1">
         <v>187.62</v>
       </c>
-      <c r="C42" t="s">
-        <v>21</v>
+      <c r="C42">
+        <v>2023</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.5">
@@ -1196,8 +1181,8 @@
       <c r="B43" s="1">
         <v>60.94</v>
       </c>
-      <c r="C43" t="s">
-        <v>21</v>
+      <c r="C43">
+        <v>2023</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.5">
@@ -1207,8 +1192,8 @@
       <c r="B44" s="1">
         <v>37.81</v>
       </c>
-      <c r="C44" t="s">
-        <v>21</v>
+      <c r="C44">
+        <v>2023</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.5">
@@ -1218,8 +1203,8 @@
       <c r="B45" s="1">
         <v>153.49</v>
       </c>
-      <c r="C45" t="s">
-        <v>21</v>
+      <c r="C45">
+        <v>2023</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.5">
@@ -1229,8 +1214,8 @@
       <c r="B46" s="2">
         <v>47.1</v>
       </c>
-      <c r="C46" t="s">
-        <v>21</v>
+      <c r="C46">
+        <v>2023</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.5">
@@ -1240,8 +1225,8 @@
       <c r="B47" s="2">
         <v>53.53</v>
       </c>
-      <c r="C47" t="s">
-        <v>21</v>
+      <c r="C47">
+        <v>2023</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.5">
@@ -1251,8 +1236,8 @@
       <c r="B48" s="2">
         <v>233.83</v>
       </c>
-      <c r="C48" t="s">
-        <v>21</v>
+      <c r="C48">
+        <v>2023</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.5">
@@ -1262,8 +1247,8 @@
       <c r="B49" s="1">
         <v>232.25</v>
       </c>
-      <c r="C49" t="s">
-        <v>19</v>
+      <c r="C49">
+        <v>2024</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.5">
@@ -1273,8 +1258,8 @@
       <c r="B50" s="1">
         <v>91.05</v>
       </c>
-      <c r="C50" t="s">
-        <v>19</v>
+      <c r="C50">
+        <v>2024</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.5">
@@ -1284,8 +1269,8 @@
       <c r="B51" s="1">
         <v>152.15</v>
       </c>
-      <c r="C51" t="s">
-        <v>19</v>
+      <c r="C51">
+        <v>2024</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.5">
@@ -1295,8 +1280,8 @@
       <c r="B52" s="1">
         <v>151.52000000000001</v>
       </c>
-      <c r="C52" t="s">
-        <v>19</v>
+      <c r="C52">
+        <v>2024</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.5">
@@ -1306,8 +1291,8 @@
       <c r="B53" s="1">
         <v>465.12</v>
       </c>
-      <c r="C53" t="s">
-        <v>19</v>
+      <c r="C53">
+        <v>2024</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.5">
@@ -1317,8 +1302,8 @@
       <c r="B54" s="1">
         <v>66.760000000000005</v>
       </c>
-      <c r="C54" t="s">
-        <v>19</v>
+      <c r="C54">
+        <v>2024</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.5">
@@ -1328,8 +1313,8 @@
       <c r="B55" s="1">
         <v>27.04</v>
       </c>
-      <c r="C55" t="s">
-        <v>19</v>
+      <c r="C55">
+        <v>2024</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.5">
@@ -1339,8 +1324,8 @@
       <c r="B56" s="1">
         <v>205.9</v>
       </c>
-      <c r="C56" t="s">
-        <v>19</v>
+      <c r="C56">
+        <v>2024</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.5">
@@ -1350,8 +1335,8 @@
       <c r="B57" s="2">
         <v>98.18</v>
       </c>
-      <c r="C57" t="s">
-        <v>19</v>
+      <c r="C57">
+        <v>2024</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.5">
@@ -1361,8 +1346,8 @@
       <c r="B58" s="2">
         <v>119.76</v>
       </c>
-      <c r="C58" t="s">
-        <v>19</v>
+      <c r="C58">
+        <v>2024</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.5">
@@ -1372,8 +1357,8 @@
       <c r="B59" s="2">
         <v>65.319999999999993</v>
       </c>
-      <c r="C59" t="s">
-        <v>19</v>
+      <c r="C59">
+        <v>2024</v>
       </c>
     </row>
   </sheetData>
